--- a/Flag/Flagar/resultado_flag.xlsx
+++ b/Flag/Flagar/resultado_flag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,51 +456,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>94639182</t>
+          <t>95284508</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>já existe</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>86546118</t>
+          <t>95365565</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -522,56 +514,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>86779944</t>
+          <t>95433452</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>já existe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>83316196</t>
+          <t>95648252</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>flagado</t>
+          <t>já existe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -588,150 +572,130 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81792864</t>
+          <t>96300496</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>94028248</t>
+          <t>96305022</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emagrecimento</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>95488776</t>
+          <t>96534719</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Insuficiência Cardíaca Controlada</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93476514</t>
+          <t>96561700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Insuficiência Cardíaca Controlada</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76904727</t>
+          <t>96596045</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -753,495 +717,203 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Insuficiência Cardíaca Controlada</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>115720162</t>
+          <t>96659511</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>falha crítica</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Insuficiência Cardíaca Controlada</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>222557966</t>
+          <t>96985666</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>falha crítica</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anticoagulante Seguro</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>789823306</t>
+          <t>97164816</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>mensagem após enter</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anticoagulante Seguro</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>85039945</t>
+          <t>451215559</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>mensagem após enter</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cuidados Pós Infarto</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>906839661</t>
+          <t>451566114</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>sem adicionar</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Excluído</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cuidados Pós Infarto</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>593931173</t>
+          <t>594082986</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>falha crítica</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cuidados Pós Infarto</t>
+          <t>Viva Bem - Dom Pedro</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>190635789</t>
+          <t>882001140</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>falha crítica</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Erro</t>
+          <t>Ativo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Erro</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cuidados Pós Infarto</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>745678793</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>falha crítica</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Erro</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Erro</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>81646677</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>sem adicionar</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>93116574</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>sem adicionar</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>86948624</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>mensagem após enter</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>82015735</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>mensagem após enter</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>94835103</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>mensagem após enter</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>92906207</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>mensagem após enter</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Saúde da Coluna</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>46183</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>83633828</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>mensagem após enter</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Excluído</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>

--- a/Flag/Flagar/resultado_flag.xlsx
+++ b/Flag/Flagar/resultado_flag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,19 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidado Cardíaco Valvar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>95284508</t>
+          <t>92865919</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>já existe</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -485,19 +489,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidados para Endometriose</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>95365565</t>
+          <t>95743588</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>já existe</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -514,19 +522,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidados para Endometriose</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>95433452</t>
+          <t>94651557</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>já existe</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -543,19 +555,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidados para Endometriose</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>95648252</t>
+          <t>92897609</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>já existe</t>
+          <t>flagado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,14 +588,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidados para Endometriose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>96300496</t>
+          <t>97713347</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -601,14 +621,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Cuidados Pós Infarto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>96305022</t>
+          <t>97760180</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -630,14 +654,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Emagrecimento</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>96534719</t>
+          <t>92998114</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -659,14 +687,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Emagrecimento</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>96561700</t>
+          <t>96782963</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -688,14 +720,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Emagrecimento</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>96596045</t>
+          <t>96637052</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -717,14 +753,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Emagrecimento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>96659511</t>
+          <t>97050888</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -746,14 +786,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Gestação Segura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>96985666</t>
+          <t>95074125</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -775,14 +819,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Gestação Segura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>97164816</t>
+          <t>96252961</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -804,14 +852,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Insuficiência Cardíaca Controlada</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>451215559</t>
+          <t>93512690</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -833,14 +885,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Insuficiência Cardíaca Controlada</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>451566114</t>
+          <t>451929845</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -862,14 +918,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Ritmo Certo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>594082986</t>
+          <t>83617517</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -891,14 +951,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Viva Bem - Dom Pedro</t>
+          <t>Saúde da Coluna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>882001140</t>
+          <t>95711553</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -912,6 +976,270 @@
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>95710405</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>94722467</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>89990991</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>93823257</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>82929624</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>97864805</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>85304054</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>95739111</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>flagado</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
